--- a/data/demo/demo_trial_balance_5years.xlsx
+++ b/data/demo/demo_trial_balance_5years.xlsx
@@ -423,6 +423,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -493,7 +494,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BS 3.1.3.2</t>
+          <t>BS 03.01.03.02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BS 3.1.3.1</t>
+          <t>BS 03.01.03.01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,7 +548,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BS 3.1.3.2</t>
+          <t>BS 03.01.03.02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -574,7 +575,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BS 3.1.3.1</t>
+          <t>BS 03.01.03.01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,7 +602,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BS 3.1.2.1</t>
+          <t>BS 03.01.02.01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -628,7 +629,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BS 3.1.1.4</t>
+          <t>BS 03.01.01.04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -653,7 +654,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>GOODS IN TRANSIT</t>
@@ -678,7 +678,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BS 3.2.4</t>
+          <t>BS 03.02.04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BS 3.1.2.2</t>
+          <t>BS 03.01.02.02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BS 1.08</t>
+          <t>BS 01.07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BS 1.09</t>
+          <t>BS 01.10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -792,7 +792,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BS 1.07</t>
+          <t>BS 01.08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BS 1.09</t>
+          <t>BS 01.10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BS 1.03</t>
+          <t>BS 01.03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BS 1.09</t>
+          <t>BS 01.10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BS 1.08</t>
+          <t>BS 01.09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BS 1.09</t>
+          <t>BS 01.10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BS 8.1.1</t>
+          <t>BS 08.01.01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BS 8.1.6</t>
+          <t>BS 08.01.06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BS 8.1.6</t>
+          <t>BS 08.01.06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1051,7 +1051,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>RSSB CONTRIBUTIONS PAYABLES</t>
@@ -1076,7 +1075,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BS 6.2.2</t>
+          <t>BS 06.02.02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,7 +1102,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BS 5.01</t>
+          <t>BS 05.01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,7 +1129,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BS 5.07</t>
+          <t>BS 05.07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1164,7 +1163,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PL 1.1</t>
+          <t>PL 01.01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1196,7 +1195,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PL 1.1</t>
+          <t>PL 01.01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1228,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PL 2.2.1</t>
+          <t>PL 02.02.01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1255,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PL 6.06</t>
+          <t>PL 06.04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1282,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PL 5.01</t>
+          <t>PL 05.01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1309,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PL 5.01</t>
+          <t>PL 05.01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1336,7 +1335,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PL 5.01</t>
+          <t>PL 05.01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1363,7 +1362,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PL 5.01</t>
+          <t>PL 05.01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1390,7 +1389,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PL 4.27</t>
+          <t>PL 04.27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1415,7 +1414,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>Trading Lisence/No crreance/other administative document</t>
@@ -1440,7 +1438,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PL 4.27</t>
+          <t>PL 04.27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1467,7 +1465,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PL 4.16</t>
+          <t>PL 04.16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1494,7 +1492,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PL 5.10</t>
+          <t>PL 05.08.02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1521,7 +1519,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PL 6.08</t>
+          <t>PL 06.06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1548,7 +1546,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PL 4.27</t>
+          <t>PL 04.27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1575,7 +1573,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PL 7.02</t>
+          <t>PL 07.02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1602,7 +1600,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BS 6.1.4</t>
+          <t>BS 06.01.04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1619,7 +1617,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BS 3.1.4</t>
+          <t>BS 03.01.04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
